--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486542_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486542_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2272</v>
+        <v>7.3351</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3165</v>
+        <v>5.7636</v>
       </c>
       <c r="F2" t="n">
-        <v>1.9106</v>
+        <v>1.5716</v>
       </c>
       <c r="G2" t="n">
         <v>6.1758</v>
@@ -610,13 +610,13 @@
         <v>1.0875</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0362</v>
+        <v>0.0718</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.822</v>
+        <v>-0.3749</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.4467</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3656</v>
+        <v>3.7413</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5702</v>
+        <v>3.3467</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7953</v>
+        <v>0.3946</v>
       </c>
       <c r="G3" t="n">
         <v>3.2779</v>
@@ -688,13 +688,13 @@
         <v>1.0875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7603</v>
+        <v>0.1361</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2824</v>
+        <v>-0.5059</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0427</v>
+        <v>0.642</v>
       </c>
       <c r="V3" t="n">
         <v>-0.7602</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. VRANKIC</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.698</v>
+        <v>3.7229</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8168</v>
+        <v>2.928</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8812</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.3402</v>
+        <v>2.1892</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6431</v>
+        <v>-1.1345</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.3029</v>
+        <v>3.3237</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1659</v>
+        <v>2.7814</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5795</v>
+        <v>-1.1981</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.4136</v>
+        <v>3.9795</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8257</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="N4" t="n">
         <v>0.0636</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8893</v>
+        <v>-0.6558</v>
       </c>
       <c r="P4" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.87</v>
+        <v>1.305</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6183</v>
+        <v>0.2286</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3257</v>
+        <v>0.1466</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2926</v>
+        <v>0.082</v>
       </c>
       <c r="V4" t="n">
-        <v>1.8695</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5443</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.613</v>
+        <v>3.689</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5733</v>
+        <v>4.0218</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0397</v>
+        <v>-0.3328</v>
       </c>
       <c r="G5" t="n">
-        <v>1.1672</v>
+        <v>4.0638</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5265</v>
+        <v>1.98</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6407</v>
+        <v>2.0838</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3434</v>
+        <v>4.3691</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5784</v>
+        <v>1.8828</v>
       </c>
       <c r="L5" t="n">
-        <v>0.765</v>
+        <v>2.4862</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1762</v>
+        <v>-0.3053</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0519</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1243</v>
+        <v>-0.4024</v>
       </c>
       <c r="P5" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5105</v>
+        <v>0.1027</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5997</v>
+        <v>0.1971</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9109</v>
+        <v>-0.09429999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3698</v>
+        <v>-1.13</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3698</v>
+        <v>-0.5443</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5857</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>J. VRANKIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.5041</v>
+        <v>3.2086</v>
       </c>
       <c r="E6" t="n">
-        <v>4.0218</v>
+        <v>2.4815</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5177</v>
+        <v>0.7271</v>
       </c>
       <c r="G6" t="n">
-        <v>4.0638</v>
+        <v>0.3402</v>
       </c>
       <c r="H6" t="n">
-        <v>1.98</v>
+        <v>2.6431</v>
       </c>
       <c r="I6" t="n">
-        <v>2.0838</v>
+        <v>-2.3029</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3691</v>
+        <v>1.1659</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8828</v>
+        <v>2.5795</v>
       </c>
       <c r="L6" t="n">
-        <v>2.4862</v>
+        <v>-1.4136</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3053</v>
+        <v>-0.8257</v>
       </c>
       <c r="N6" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.0636</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4024</v>
+        <v>-0.8893</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0822</v>
+        <v>0.1289</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1971</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2793</v>
+        <v>0.1385</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.13</v>
+        <v>1.8695</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.5443</v>
+        <v>1.3252</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5857</v>
+        <v>0.5443</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.1603</v>
+        <v>2.5224</v>
       </c>
       <c r="E7" t="n">
-        <v>2.7045</v>
+        <v>0.791</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4558</v>
+        <v>1.7315</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1892</v>
+        <v>1.1672</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1345</v>
+        <v>0.5265</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3237</v>
+        <v>0.6407</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7814</v>
+        <v>1.3434</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1981</v>
+        <v>0.5784</v>
       </c>
       <c r="L7" t="n">
-        <v>3.9795</v>
+        <v>0.765</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5921999999999999</v>
+        <v>-0.1762</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0636</v>
+        <v>-0.0519</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6558</v>
+        <v>-0.1243</v>
       </c>
       <c r="P7" t="n">
         <v>1.305</v>
@@ -1000,19 +1000,19 @@
         <v>1.305</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.334</v>
+        <v>0.42</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0769</v>
+        <v>-0.1826</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2571</v>
+        <v>0.6026</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3698</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7187</v>
+        <v>0.4335</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8652</v>
+        <v>0.6417</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1465</v>
+        <v>-0.2082</v>
       </c>
       <c r="G8" t="n">
         <v>1.3438</v>
@@ -1078,13 +1078,13 @@
         <v>0.2175</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2449</v>
+        <v>-0.0403</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4711</v>
+        <v>0.2476</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2262</v>
+        <v>-0.2878</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. GOMEZ FERNANDEZ</t>
+          <t>M. RODRIGUEZ BARRIENTOS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.08890000000000001</v>
+        <v>0.4195</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.0805</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.008399999999999999</v>
+        <v>0.5069</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.2105</v>
+        <v>-0.671</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1338</v>
+        <v>1.3928</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3442</v>
+        <v>-2.0638</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0565</v>
+        <v>-0.3458</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0182</v>
+        <v>0.5506</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0382</v>
+        <v>-0.8964</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.267</v>
+        <v>-0.3252</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1155</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3825</v>
+        <v>-1.1674</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0959</v>
+        <v>-0.2145</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.137</v>
+        <v>0.2584</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0411</v>
+        <v>-0.4729</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. RODRIGUEZ BARRIENTOS</t>
+          <t>O. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1007</v>
+        <v>-0.0272</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4227</v>
+        <v>-0.0805</v>
       </c>
       <c r="F10" t="n">
-        <v>0.322</v>
+        <v>0.0533</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.671</v>
+        <v>-0.2105</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3928</v>
+        <v>0.1338</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0638</v>
+        <v>-0.3442</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3458</v>
+        <v>0.0565</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5506</v>
+        <v>0.0182</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8964</v>
+        <v>0.0382</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.3252</v>
+        <v>-0.267</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.1155</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.1674</v>
+        <v>-0.3825</v>
       </c>
       <c r="P10" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7347</v>
+        <v>-0.0342</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0769</v>
+        <v>-0.137</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6578000000000001</v>
+        <v>0.1027</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.2185</v>
+        <v>-0.1376</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4092</v>
+        <v>-0.2974</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1907</v>
+        <v>0.1598</v>
       </c>
       <c r="G11" t="n">
         <v>1.3366</v>
@@ -1312,13 +1312,13 @@
         <v>0.6525</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0326</v>
+        <v>0.0484</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2139</v>
+        <v>-0.1021</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1813</v>
+        <v>0.1505</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.319</v>
+        <v>-2.1341</v>
       </c>
       <c r="E12" t="n">
         <v>-0.8585</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4605</v>
+        <v>-1.2756</v>
       </c>
       <c r="G12" t="n">
         <v>1.6262</v>
@@ -1390,13 +1390,13 @@
         <v>0.87</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3802</v>
+        <v>-0.1953</v>
       </c>
       <c r="T12" t="n">
         <v>0.1971</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5773</v>
+        <v>-0.3924</v>
       </c>
       <c r="V12" t="n">
         <v>-2.2599</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3332</v>
+        <v>-3.5471</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3237</v>
+        <v>-4.8767</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9905</v>
+        <v>1.3296</v>
       </c>
       <c r="G13" t="n">
         <v>-2.3944</v>
@@ -1468,13 +1468,13 @@
         <v>1.305</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8735000000000001</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.548</v>
+        <v>-0.1009</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3255</v>
+        <v>0.0135</v>
       </c>
       <c r="V13" t="n">
         <v>-0.1952</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>19.2266</v>
+        <v>19.2263</v>
       </c>
       <c r="E14" t="n">
-        <v>13.77370000000001</v>
+        <v>13.7738</v>
       </c>
       <c r="F14" t="n">
-        <v>5.452699999999999</v>
+        <v>5.452700000000001</v>
       </c>
       <c r="G14" t="n">
         <v>18.2448</v>
@@ -1516,7 +1516,7 @@
         <v>14.8421</v>
       </c>
       <c r="I14" t="n">
-        <v>3.4027</v>
+        <v>3.402700000000001</v>
       </c>
       <c r="J14" t="n">
         <v>21.3419</v>
@@ -1528,7 +1528,7 @@
         <v>10.2836</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0971</v>
+        <v>-3.097099999999999</v>
       </c>
       <c r="N14" t="n">
         <v>3.7839</v>
@@ -1537,7 +1537,7 @@
         <v>-6.881</v>
       </c>
       <c r="P14" t="n">
-        <v>3.262499999999999</v>
+        <v>3.2625</v>
       </c>
       <c r="Q14" t="n">
         <v>-7.6128</v>
@@ -1546,13 +1546,13 @@
         <v>10.875</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5647000000000001</v>
+        <v>0.5647999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3664000000000001</v>
+        <v>-0.3662</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9312000000000004</v>
+        <v>0.9311000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-2.8456</v>
@@ -1561,7 +1561,7 @@
         <v>0.4110999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-3.2567</v>
+        <v>-3.256699999999999</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.1034</v>
+        <v>3.2538</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3155</v>
+        <v>4.6507</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.212</v>
+        <v>-1.397</v>
       </c>
       <c r="G15" t="n">
         <v>1.9135</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0822</v>
+        <v>0.2325</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2704</v>
+        <v>0.0649</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3526</v>
+        <v>0.1676</v>
       </c>
       <c r="V15" t="n">
         <v>1.3252</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTINEZ CABEZUDO</t>
+          <t>L. CAPALBO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.6241</v>
+        <v>-0.5802</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0745</v>
+        <v>0.4343</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.6986</v>
+        <v>-1.0144</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8484</v>
+        <v>1.8839</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2707</v>
+        <v>0.0941</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.5777</v>
+        <v>1.7897</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3485</v>
+        <v>3.34</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3102</v>
+        <v>1.0434</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0382</v>
+        <v>2.2966</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1969</v>
+        <v>-1.4561</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.581</v>
+        <v>-0.9493</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.616</v>
+        <v>-0.5068</v>
       </c>
       <c r="P16" t="n">
-        <v>0.2175</v>
+        <v>-1.305</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2175</v>
+        <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0068</v>
+        <v>-0.9638</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.274</v>
+        <v>-0.7306</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2808</v>
+        <v>-0.2331</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>J. MARTINEZ CABEZUDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3625</v>
+        <v>-0.7166</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.0698</v>
+        <v>0.0745</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.2927</v>
+        <v>-0.7911</v>
       </c>
       <c r="G17" t="n">
-        <v>-4.3994</v>
+        <v>-0.8484</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.4336</v>
+        <v>-0.2707</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9658</v>
+        <v>-0.5777</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.6308</v>
+        <v>0.3485</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.9368</v>
+        <v>0.3102</v>
       </c>
       <c r="L17" t="n">
-        <v>0.306</v>
+        <v>0.0382</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.7686</v>
+        <v>-1.1969</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.4967</v>
+        <v>-0.581</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2718</v>
+        <v>-0.616</v>
       </c>
       <c r="P17" t="n">
         <v>0.2175</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.305</v>
+        <v>0.2175</v>
       </c>
       <c r="S17" t="n">
-        <v>3.3637</v>
+        <v>-0.0856</v>
       </c>
       <c r="T17" t="n">
-        <v>2.3674</v>
+        <v>-0.274</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9963</v>
+        <v>0.1884</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5443</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.7188</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. CAPALBO</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5088</v>
+        <v>-0.7965</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1245</v>
+        <v>-1.1857</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3843</v>
+        <v>0.3892</v>
       </c>
       <c r="G18" t="n">
-        <v>1.8839</v>
+        <v>-1.9879</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0941</v>
+        <v>-1.0859</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7897</v>
+        <v>-0.902</v>
       </c>
       <c r="J18" t="n">
-        <v>3.34</v>
+        <v>-1.0793</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0434</v>
+        <v>-0.8331</v>
       </c>
       <c r="L18" t="n">
-        <v>2.2966</v>
+        <v>-0.2462</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4561</v>
+        <v>-0.9086</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9493</v>
+        <v>-0.2528</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5068</v>
+        <v>-0.6558</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.305</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.87</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.8924</v>
+        <v>-0.2659</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2894</v>
+        <v>-0.3016</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.603</v>
+        <v>0.0357</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1952</v>
+        <v>0.3698</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5704</v>
+        <v>-1.2428</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.524</v>
+        <v>-0.4122</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0464</v>
+        <v>-0.8306</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7312</v>
@@ -1936,13 +1936,13 @@
         <v>0.87</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6216</v>
+        <v>-0.2941</v>
       </c>
       <c r="T19" t="n">
-        <v>0.08409999999999999</v>
+        <v>0.1959</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7058</v>
+        <v>-0.49</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>B. VAZQUEZ ARRAIZA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6097</v>
+        <v>-2.8032</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.968</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3584</v>
+        <v>-2.1172</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9879</v>
+        <v>-0.1597</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0859</v>
+        <v>-0.0609</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.902</v>
+        <v>-0.0988</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.0793</v>
+        <v>2.0876</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8331</v>
+        <v>1.168</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2462</v>
+        <v>0.9196</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9086</v>
+        <v>-2.2473</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2528</v>
+        <v>-1.2289</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6558</v>
+        <v>-1.0184</v>
       </c>
       <c r="P20" t="n">
-        <v>1.0875</v>
+        <v>-1.9576</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.079</v>
+        <v>-0.6859</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0839</v>
+        <v>-0.5984</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0049</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.1745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B. VAZQUEZ ARRAIZA</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2424</v>
+        <v>-3.2855</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9095</v>
+        <v>-2.4703</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.333</v>
+        <v>-0.8152</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1597</v>
+        <v>-5.2462</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0609</v>
+        <v>-2.7918</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0988</v>
+        <v>-2.4543</v>
       </c>
       <c r="J21" t="n">
-        <v>2.0876</v>
+        <v>-3.7288</v>
       </c>
       <c r="K21" t="n">
-        <v>1.168</v>
+        <v>-2.1439</v>
       </c>
       <c r="L21" t="n">
-        <v>0.9196</v>
+        <v>-1.5849</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.2473</v>
+        <v>-1.5173</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.2289</v>
+        <v>-0.6479</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0184</v>
+        <v>-0.8694</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.9576</v>
+        <v>0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2175</v>
+        <v>0.6525</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1251</v>
+        <v>0.1782</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.822</v>
+        <v>0.1286</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3032</v>
+        <v>0.0496</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.378</v>
+        <v>-4.0445</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.4703</v>
+        <v>-2.858</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9077</v>
+        <v>-1.1866</v>
       </c>
       <c r="G22" t="n">
-        <v>-5.2462</v>
+        <v>-4.3994</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.7918</v>
+        <v>-3.4336</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.4543</v>
+        <v>-0.9658</v>
       </c>
       <c r="J22" t="n">
-        <v>-3.7288</v>
+        <v>-1.6308</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.1439</v>
+        <v>-1.9368</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.5849</v>
+        <v>0.306</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.5173</v>
+        <v>-2.7686</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6479</v>
+        <v>-1.4967</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8694</v>
+        <v>-1.2718</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6525</v>
+        <v>0.2175</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R22" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0857</v>
+        <v>0.6817</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1286</v>
+        <v>0.5792</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0429</v>
+        <v>0.1024</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>-0.5443</v>
       </c>
       <c r="W22" t="n">
-        <v>1.13</v>
+        <v>-0.7188</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.1745</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. NIANG BEYE</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5167</v>
+        <v>-4.3653</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.6667</v>
+        <v>-2.0671</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.8499</v>
+        <v>-2.2982</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.7653</v>
+        <v>-4.904</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.6401</v>
+        <v>-1.6943</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1252</v>
+        <v>-3.2097</v>
       </c>
       <c r="J23" t="n">
-        <v>0.0129</v>
+        <v>-1.8199</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5808</v>
+        <v>-0.5626</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5937</v>
+        <v>-1.2574</v>
       </c>
       <c r="M23" t="n">
-        <v>-3.7782</v>
+        <v>-3.0841</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.0593</v>
+        <v>-1.1318</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7188</v>
+        <v>-1.9523</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.5225</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>-1.0875</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6525</v>
+        <v>0.87</v>
       </c>
       <c r="S23" t="n">
-        <v>2.1409</v>
+        <v>-0.3737</v>
       </c>
       <c r="T23" t="n">
-        <v>1.3003</v>
+        <v>-0.2896</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8407</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3698</v>
+        <v>1.13</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1952</v>
+        <v>1.13</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5649999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>S. NIANG BEYE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.5175</v>
+        <v>-4.6458</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.8494</v>
+        <v>-1.6726</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6681</v>
+        <v>-2.9732</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.904</v>
+        <v>-3.7653</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.6943</v>
+        <v>-2.6401</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.2097</v>
+        <v>-1.1252</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8199</v>
+        <v>0.0129</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5626</v>
+        <v>-0.5808</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2574</v>
+        <v>0.5937</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.0841</v>
+        <v>-3.7782</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.1318</v>
+        <v>-2.0593</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.9523</v>
+        <v>-1.7188</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>0.87</v>
+        <v>0.6525</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5259</v>
+        <v>1.0118</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0719</v>
+        <v>0.2944</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.454</v>
+        <v>0.7174</v>
       </c>
       <c r="V24" t="n">
-        <v>1.13</v>
+        <v>-0.3698</v>
       </c>
       <c r="W24" t="n">
-        <v>1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -2359,10 +2359,10 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.2267</v>
+        <v>-19.2266</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.192200000000001</v>
+        <v>-6.192400000000001</v>
       </c>
       <c r="F25" t="n">
         <v>-13.0343</v>
@@ -2377,13 +2377,13 @@
         <v>-3.4025</v>
       </c>
       <c r="J25" t="n">
-        <v>3.0973</v>
+        <v>3.097299999999999</v>
       </c>
       <c r="K25" t="n">
         <v>-3.7839</v>
       </c>
       <c r="L25" t="n">
-        <v>6.881099999999998</v>
+        <v>6.8811</v>
       </c>
       <c r="M25" t="n">
         <v>-21.3419</v>
@@ -2404,13 +2404,13 @@
         <v>7.6125</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5647000000000004</v>
+        <v>-0.5648</v>
       </c>
       <c r="T25" t="n">
         <v>-0.9312000000000002</v>
       </c>
       <c r="U25" t="n">
-        <v>0.3664</v>
+        <v>0.3665</v>
       </c>
       <c r="V25" t="n">
         <v>2.845699999999999</v>
